--- a/inventory/files/2026-W42/STA_US_AUTO_2026-W42.xlsx
+++ b/inventory/files/2026-W42/STA_US_AUTO_2026-W42.xlsx
@@ -1536,7 +1536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="28" min="1" max="1"/>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79170</v>
+        <v>67305</v>
       </c>
       <c r="C9" t="n">
         <v>105</v>
       </c>
       <c r="D9" t="n">
-        <v>754</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8459</v>
+        <v>8693</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6597</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="12">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5824</v>
+        <v>5052</v>
       </c>
     </row>
     <row r="13">
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3300</v>
+        <v>2100</v>
       </c>
       <c r="C13" t="n">
         <v>150</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1754,125 +1754,131 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1739</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AH-828A</t>
+          <t>AH-PROPAINTKITA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1350</v>
+        <v>776</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AH-RCWHL14A</t>
+          <t>AH-828A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1050</v>
+        <v>510</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AH-TRPROAUPC</t>
+          <t>AH-RCPL-QA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>779</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AH-PROPAINTKITA</t>
+          <t>AH-RCWHL14A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>768</v>
-      </c>
-      <c r="C18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>96</v>
+        <v>466</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AH-RCTIRE-QA</t>
+          <t>AH-TRPROAUPC</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>511</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AH-RCPL-QA</t>
+          <t>AH-VEHSHAM16A</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>483</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AH-SPONGE3A</t>
+          <t>AH-RCINT14-2PA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>366</v>
+        <v>204</v>
+      </c>
+      <c r="C21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AH-RCPAINTQA</t>
+          <t>AH-PROPTKTPP16A</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>245</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AH-RCINT14-2PA</t>
+          <t>AH-RCPV14A</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>180</v>
-      </c>
-      <c r="C23" t="n">
-        <v>12</v>
-      </c>
-      <c r="D23" t="n">
-        <v>15</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AH-VEHSHAM16A</t>
+          <t>AH-FOAMAPP3</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168</v>
+        <v>120</v>
+      </c>
+      <c r="C24" t="n">
+        <v>120</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1882,36 +1888,42 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C25" t="n">
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AH-RCPV14A</t>
+          <t>AH-811A</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>145</v>
+        <v>56</v>
+      </c>
+      <c r="C26" t="n">
+        <v>14</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AH-FOAMAPP3</t>
+          <t>AH-MFDRYTWLA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1920,30 +1932,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AH-PROMARKITA</t>
+          <t>AH-RCINT-QA</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AH-811A</t>
+          <t>AH-PROPVKITA</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
@@ -1952,14 +1964,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AH-MFDRYTWLA</t>
+          <t>AH-PROWHLKITA</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -1968,65 +1980,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AH-GCLEAN-B16A</t>
+          <t>AH-RCPV-QA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C31" t="n">
-        <v>20</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AH-RCINT-QA</t>
+          <t>AH-BNDL-COREA</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AH-RCACA</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>20</v>
-      </c>
-      <c r="C33" t="n">
-        <v>20</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AH-PROPVKITA</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>8</v>
-      </c>
-      <c r="C34" t="n">
-        <v>8</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
